--- a/Rubric.xlsx
+++ b/Rubric.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{4C64B3E2-D3B6-48C7-907F-6C785E575285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{32588BC0-C28F-4FE7-8334-555E261918CC}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{32588BC0-C28F-4FE7-8334-555E261918CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
